--- a/datacontrol/veh_details.xlsx
+++ b/datacontrol/veh_details.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aipc1\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\Survilance_System\datacontrol\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C0ED164-24B1-41B6-B723-A36AFB31684F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17250" windowHeight="5850"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2517" uniqueCount="932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2598" uniqueCount="962">
   <si>
     <t>S.NO</t>
   </si>
@@ -2831,12 +2830,102 @@
   </si>
   <si>
     <t>TATA SAFARI</t>
+  </si>
+  <si>
+    <t>25B144476Y</t>
+  </si>
+  <si>
+    <t>HQ 142 INF BDE</t>
+  </si>
+  <si>
+    <t>24B142938W</t>
+  </si>
+  <si>
+    <t>24B142311W</t>
+  </si>
+  <si>
+    <t>20B135922K</t>
+  </si>
+  <si>
+    <t>21B136473E</t>
+  </si>
+  <si>
+    <t>20A073277Y</t>
+  </si>
+  <si>
+    <t>20A073276E</t>
+  </si>
+  <si>
+    <t>20A072830N</t>
+  </si>
+  <si>
+    <t>21D210541E</t>
+  </si>
+  <si>
+    <t>21D210561N</t>
+  </si>
+  <si>
+    <t>21D210594H</t>
+  </si>
+  <si>
+    <t>21C109318M</t>
+  </si>
+  <si>
+    <t>21C109319K</t>
+  </si>
+  <si>
+    <t>20C108600N</t>
+  </si>
+  <si>
+    <t>20P033548P</t>
+  </si>
+  <si>
+    <t>315 FD WKSP COY</t>
+  </si>
+  <si>
+    <t>20B134348K</t>
+  </si>
+  <si>
+    <t>20B134347M</t>
+  </si>
+  <si>
+    <t>20P033474Y</t>
+  </si>
+  <si>
+    <t>21C109336K</t>
+  </si>
+  <si>
+    <t>21C109337E</t>
+  </si>
+  <si>
+    <t>20D209843E</t>
+  </si>
+  <si>
+    <t>20D209958N</t>
+  </si>
+  <si>
+    <t>20D209954K</t>
+  </si>
+  <si>
+    <t>00P013450K</t>
+  </si>
+  <si>
+    <t>20P033698Y</t>
+  </si>
+  <si>
+    <t>25R012559W</t>
+  </si>
+  <si>
+    <t>25R012580N</t>
+  </si>
+  <si>
+    <t>2.5 TON TATA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -3208,9 +3297,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:D991"/>
+  <dimension ref="A1:D990"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="4" bestFit="1" customWidth="1"/>
@@ -14978,167 +15067,379 @@
       <c r="A842" s="3">
         <v>839</v>
       </c>
-      <c r="B842" s="2"/>
-      <c r="C842" s="2"/>
-      <c r="D842" s="2"/>
+      <c r="B842" s="2" t="s">
+        <v>932</v>
+      </c>
+      <c r="C842" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D842" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="843" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A843" s="3">
         <v>840</v>
       </c>
-      <c r="B843" s="2"/>
-      <c r="C843" s="2"/>
-      <c r="D843" s="2"/>
+      <c r="B843" s="2" t="s">
+        <v>934</v>
+      </c>
+      <c r="C843" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D843" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="844" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A844" s="3"/>
-      <c r="B844" s="2"/>
-      <c r="C844" s="2"/>
-      <c r="D844" s="2"/>
+      <c r="A844" s="3">
+        <v>841</v>
+      </c>
+      <c r="B844" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="C844" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D844" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="845" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A845" s="3"/>
-      <c r="B845" s="2"/>
-      <c r="C845" s="2"/>
-      <c r="D845" s="2"/>
+      <c r="A845" s="3">
+        <v>842</v>
+      </c>
+      <c r="B845" s="2" t="s">
+        <v>936</v>
+      </c>
+      <c r="C845" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D845" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="846" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A846" s="3"/>
-      <c r="B846" s="2"/>
-      <c r="C846" s="2"/>
-      <c r="D846" s="2"/>
+      <c r="A846" s="3">
+        <v>843</v>
+      </c>
+      <c r="B846" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="C846" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D846" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="847" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A847" s="3"/>
-      <c r="B847" s="2"/>
-      <c r="C847" s="2"/>
-      <c r="D847" s="2"/>
+      <c r="A847" s="3">
+        <v>844</v>
+      </c>
+      <c r="B847" s="2" t="s">
+        <v>938</v>
+      </c>
+      <c r="C847" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D847" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="848" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A848" s="3"/>
-      <c r="B848" s="2"/>
-      <c r="C848" s="2"/>
-      <c r="D848" s="2"/>
+      <c r="A848" s="3">
+        <v>845</v>
+      </c>
+      <c r="B848" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="C848" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D848" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="849" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A849" s="3"/>
-      <c r="B849" s="2"/>
-      <c r="C849" s="2"/>
-      <c r="D849" s="2"/>
+      <c r="A849" s="3">
+        <v>846</v>
+      </c>
+      <c r="B849" s="2" t="s">
+        <v>940</v>
+      </c>
+      <c r="C849" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D849" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="850" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A850" s="3"/>
-      <c r="B850" s="2"/>
-      <c r="C850" s="2"/>
-      <c r="D850" s="2"/>
+      <c r="A850" s="3">
+        <v>847</v>
+      </c>
+      <c r="B850" s="2" t="s">
+        <v>941</v>
+      </c>
+      <c r="C850" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D850" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="851" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A851" s="3"/>
-      <c r="B851" s="2"/>
-      <c r="C851" s="2"/>
-      <c r="D851" s="2"/>
+      <c r="A851" s="3">
+        <v>848</v>
+      </c>
+      <c r="B851" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="C851" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D851" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="852" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A852" s="3"/>
-      <c r="B852" s="2"/>
-      <c r="C852" s="2"/>
-      <c r="D852" s="2"/>
+      <c r="A852" s="3">
+        <v>849</v>
+      </c>
+      <c r="B852" s="2" t="s">
+        <v>943</v>
+      </c>
+      <c r="C852" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D852" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="853" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A853" s="3"/>
-      <c r="B853" s="2"/>
-      <c r="C853" s="2"/>
-      <c r="D853" s="2"/>
+      <c r="A853" s="3">
+        <v>850</v>
+      </c>
+      <c r="B853" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="C853" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D853" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="854" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A854" s="3"/>
-      <c r="B854" s="2"/>
-      <c r="C854" s="2"/>
-      <c r="D854" s="2"/>
+      <c r="A854" s="3">
+        <v>851</v>
+      </c>
+      <c r="B854" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="C854" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D854" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="855" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A855" s="3"/>
-      <c r="B855" s="2"/>
-      <c r="C855" s="2"/>
-      <c r="D855" s="2"/>
+      <c r="A855" s="3">
+        <v>852</v>
+      </c>
+      <c r="B855" s="2" t="s">
+        <v>946</v>
+      </c>
+      <c r="C855" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D855" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="856" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A856" s="3"/>
-      <c r="B856" s="2"/>
-      <c r="C856" s="2"/>
-      <c r="D856" s="2"/>
+      <c r="A856" s="3">
+        <v>853</v>
+      </c>
+      <c r="B856" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="C856" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D856" s="2" t="s">
+        <v>933</v>
+      </c>
     </row>
     <row r="857" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A857" s="3"/>
-      <c r="B857" s="2"/>
-      <c r="C857" s="2"/>
-      <c r="D857" s="2"/>
+      <c r="A857" s="3">
+        <v>854</v>
+      </c>
+      <c r="B857" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C857" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D857" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="858" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A858" s="3"/>
-      <c r="B858" s="2"/>
-      <c r="C858" s="2"/>
-      <c r="D858" s="2"/>
+      <c r="A858" s="3">
+        <v>855</v>
+      </c>
+      <c r="B858" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C858" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D858" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="859" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A859" s="3"/>
-      <c r="B859" s="2"/>
-      <c r="C859" s="2"/>
-      <c r="D859" s="2"/>
+      <c r="A859" s="3">
+        <v>856</v>
+      </c>
+      <c r="B859" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="C859" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="D859" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="860" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A860" s="3"/>
-      <c r="B860" s="2"/>
-      <c r="C860" s="2"/>
-      <c r="D860" s="2"/>
+      <c r="A860" s="3">
+        <v>857</v>
+      </c>
+      <c r="B860" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="C860" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D860" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="861" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A861" s="3"/>
-      <c r="B861" s="2"/>
-      <c r="C861" s="2"/>
-      <c r="D861" s="2"/>
+      <c r="A861" s="3">
+        <v>858</v>
+      </c>
+      <c r="B861" s="2" t="s">
+        <v>953</v>
+      </c>
+      <c r="C861" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="D861" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="862" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A862" s="3"/>
-      <c r="B862" s="2"/>
-      <c r="C862" s="2"/>
-      <c r="D862" s="2"/>
+      <c r="A862" s="3">
+        <v>859</v>
+      </c>
+      <c r="B862" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="C862" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D862" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="863" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A863" s="3"/>
-      <c r="B863" s="2"/>
-      <c r="C863" s="2"/>
-      <c r="D863" s="2"/>
+      <c r="A863" s="3">
+        <v>860</v>
+      </c>
+      <c r="B863" s="2" t="s">
+        <v>955</v>
+      </c>
+      <c r="C863" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D863" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="864" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A864" s="3"/>
-      <c r="B864" s="2"/>
-      <c r="C864" s="2"/>
-      <c r="D864" s="2"/>
+      <c r="A864" s="3">
+        <v>861</v>
+      </c>
+      <c r="B864" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="C864" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D864" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="865" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A865" s="3"/>
-      <c r="B865" s="2"/>
-      <c r="C865" s="2"/>
-      <c r="D865" s="2"/>
+      <c r="A865" s="3">
+        <v>862</v>
+      </c>
+      <c r="B865" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="C865" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D865" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="866" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A866" s="3"/>
-      <c r="B866" s="2"/>
-      <c r="C866" s="2"/>
-      <c r="D866" s="2"/>
+      <c r="A866" s="3">
+        <v>863</v>
+      </c>
+      <c r="B866" s="2" t="s">
+        <v>958</v>
+      </c>
+      <c r="C866" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D866" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="867" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A867" s="3"/>
-      <c r="B867" s="2"/>
-      <c r="C867" s="2"/>
-      <c r="D867" s="2"/>
+      <c r="A867" s="3">
+        <v>864</v>
+      </c>
+      <c r="B867" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="C867" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D867" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="868" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A868" s="3"/>
-      <c r="B868" s="2"/>
-      <c r="C868" s="2"/>
-      <c r="D868" s="2"/>
+      <c r="A868" s="3">
+        <v>865</v>
+      </c>
+      <c r="B868" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="C868" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D868" s="2" t="s">
+        <v>948</v>
+      </c>
     </row>
     <row r="869" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A869" s="3"/>
@@ -15871,12 +16172,6 @@
       <c r="B990" s="2"/>
       <c r="C990" s="2"/>
       <c r="D990" s="2"/>
-    </row>
-    <row r="991" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A991" s="3"/>
-      <c r="B991" s="2"/>
-      <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15889,7 +16184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7FAE30C-6445-4161-826B-74D21E9B5427}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
